--- a/artfynd/A 49421-2025 artfynd.xlsx
+++ b/artfynd/A 49421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129849016</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129849025</v>
       </c>
       <c r="B3" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129849062</v>
       </c>
       <c r="B4" t="n">
-        <v>82916</v>
+        <v>82918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49421-2025 artfynd.xlsx
+++ b/artfynd/A 49421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129849016</v>
       </c>
       <c r="B2" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129849025</v>
       </c>
       <c r="B3" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129849062</v>
       </c>
       <c r="B4" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49421-2025 artfynd.xlsx
+++ b/artfynd/A 49421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129849016</v>
       </c>
       <c r="B2" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129849025</v>
       </c>
       <c r="B3" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129849062</v>
       </c>
       <c r="B4" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49421-2025 artfynd.xlsx
+++ b/artfynd/A 49421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129849016</v>
       </c>
       <c r="B2" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129849025</v>
       </c>
       <c r="B3" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129849062</v>
       </c>
       <c r="B4" t="n">
-        <v>82924</v>
+        <v>82925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49421-2025 artfynd.xlsx
+++ b/artfynd/A 49421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129849016</v>
       </c>
       <c r="B2" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129849025</v>
       </c>
       <c r="B3" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129849062</v>
       </c>
       <c r="B4" t="n">
-        <v>82925</v>
+        <v>82931</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49421-2025 artfynd.xlsx
+++ b/artfynd/A 49421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129849016</v>
       </c>
       <c r="B2" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129849025</v>
       </c>
       <c r="B3" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49421-2025 artfynd.xlsx
+++ b/artfynd/A 49421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129849016</v>
       </c>
       <c r="B2" t="n">
-        <v>91637</v>
+        <v>91724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129849025</v>
       </c>
       <c r="B3" t="n">
-        <v>91637</v>
+        <v>91724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129849062</v>
       </c>
       <c r="B4" t="n">
-        <v>82939</v>
+        <v>83024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 49421-2025 artfynd.xlsx
+++ b/artfynd/A 49421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129849016</v>
       </c>
       <c r="B2" t="n">
-        <v>91724</v>
+        <v>91637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129849025</v>
       </c>
       <c r="B3" t="n">
-        <v>91724</v>
+        <v>91637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129849062</v>
       </c>
       <c r="B4" t="n">
-        <v>83024</v>
+        <v>82939</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
